--- a/data/distribution.xlsx
+++ b/data/distribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -53,12 +53,48 @@
   </si>
   <si>
     <t>Semaine</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Tradex</t>
+  </si>
+  <si>
+    <t>Elf</t>
+  </si>
+  <si>
+    <t>Janvier</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Avril</t>
+  </si>
+  <si>
+    <t>Samedi</t>
+  </si>
+  <si>
+    <t>Lundi</t>
+  </si>
+  <si>
+    <t>Vendredi</t>
+  </si>
+  <si>
+    <t>Jeudi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -111,11 +147,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:N1"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="1:14">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,6 +489,226 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>950</v>
+      </c>
+      <c r="E2">
+        <v>750</v>
+      </c>
+      <c r="F2">
+        <v>1150</v>
+      </c>
+      <c r="G2">
+        <v>1050</v>
+      </c>
+      <c r="H2">
+        <v>2000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>36526</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>750</v>
+      </c>
+      <c r="E3">
+        <v>760</v>
+      </c>
+      <c r="F3">
+        <v>550</v>
+      </c>
+      <c r="G3">
+        <v>980</v>
+      </c>
+      <c r="H3">
+        <v>2001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>36892</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>950</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>600</v>
+      </c>
+      <c r="G4">
+        <v>450</v>
+      </c>
+      <c r="H4">
+        <v>2002</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2">
+        <v>37414</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>650</v>
+      </c>
+      <c r="E5">
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>1050</v>
+      </c>
+      <c r="G5">
+        <v>950</v>
+      </c>
+      <c r="H5">
+        <v>2004</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
+        <v>38057</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5">
+        <v>11</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>1050</v>
+      </c>
+      <c r="E6">
+        <v>500</v>
+      </c>
+      <c r="F6">
+        <v>980</v>
+      </c>
+      <c r="G6">
+        <v>670</v>
+      </c>
+      <c r="H6">
+        <v>2005</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>38443</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/distribution.xlsx
+++ b/data/distribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -711,6 +711,226 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>950</v>
+      </c>
+      <c r="E7">
+        <v>750</v>
+      </c>
+      <c r="F7">
+        <v>1150</v>
+      </c>
+      <c r="G7">
+        <v>1050</v>
+      </c>
+      <c r="H7">
+        <v>2000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>36526</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>750</v>
+      </c>
+      <c r="E8">
+        <v>760</v>
+      </c>
+      <c r="F8">
+        <v>550</v>
+      </c>
+      <c r="G8">
+        <v>980</v>
+      </c>
+      <c r="H8">
+        <v>2001</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>36892</v>
+      </c>
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>950</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
+        <v>600</v>
+      </c>
+      <c r="G9">
+        <v>450</v>
+      </c>
+      <c r="H9">
+        <v>2002</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9" s="2">
+        <v>37414</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>650</v>
+      </c>
+      <c r="E10">
+        <v>800</v>
+      </c>
+      <c r="F10">
+        <v>1050</v>
+      </c>
+      <c r="G10">
+        <v>950</v>
+      </c>
+      <c r="H10">
+        <v>2004</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>38057</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>1050</v>
+      </c>
+      <c r="E11">
+        <v>500</v>
+      </c>
+      <c r="F11">
+        <v>980</v>
+      </c>
+      <c r="G11">
+        <v>670</v>
+      </c>
+      <c r="H11">
+        <v>2005</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>38443</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
